--- a/Result/profitability/7708.xlsx
+++ b/Result/profitability/7708.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM16"/>
+  <dimension ref="A1:AM17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2462,6 +2462,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7708</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>747</v>
+      </c>
+      <c r="D17" t="n">
+        <v>386</v>
+      </c>
+      <c r="E17" t="n">
+        <v>361</v>
+      </c>
+      <c r="F17" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="G17" t="n">
+        <v>76</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10.11%</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>72</v>
+      </c>
+      <c r="K17" t="n">
+        <v>57</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.67125</v>
+      </c>
+      <c r="N17" t="n">
+        <v>48.06375</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1614583333333333</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.6499999999999986</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.01364399664147764</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.448051948051948</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1.450000000000003</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.02915158825894659</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK17" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
